--- a/diseases/d040/2005-2009.xlsx
+++ b/diseases/d040/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18464,7 +18464,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25092,7 +25092,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26576,7 +26576,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28208,7 +28208,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29692,7 +29692,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32660,7 +32660,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34292,7 +34292,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -35776,7 +35776,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38892,7 +38892,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -42848,7 +42848,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -43936,7 +43936,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45172,7 +45172,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -47644,7 +47644,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -48732,7 +48732,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -49820,7 +49820,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -51996,7 +51996,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -53084,7 +53084,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -55112,7 +55112,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -56744,7 +56744,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -58376,7 +58376,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60008,7 +60008,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61640,7 +61640,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -63272,7 +63272,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -64904,7 +64904,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66536,7 +66536,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -68168,7 +68168,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -69652,7 +69652,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71284,7 +71284,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -72768,7 +72768,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74400,7 +74400,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -75636,7 +75636,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -76872,7 +76872,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -78108,7 +78108,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -79344,7 +79344,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
@@ -80580,7 +80580,7 @@
       </c>
       <c r="AJ440" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK440" t="inlineStr">
@@ -81668,7 +81668,7 @@
       </c>
       <c r="AJ446" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK446" t="inlineStr">
@@ -82756,7 +82756,7 @@
       </c>
       <c r="AJ452" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK452" t="inlineStr">
@@ -83992,7 +83992,7 @@
       </c>
       <c r="AJ459" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK459" t="inlineStr">
@@ -85080,7 +85080,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -86316,7 +86316,7 @@
       </c>
       <c r="AJ472" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK472" t="inlineStr">

--- a/diseases/d040/2005-2009.xlsx
+++ b/diseases/d040/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18464,7 +18464,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25092,7 +25092,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26576,7 +26576,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28208,7 +28208,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29692,7 +29692,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32660,7 +32660,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34292,7 +34292,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -35776,7 +35776,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38892,7 +38892,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -42848,7 +42848,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -43936,7 +43936,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45172,7 +45172,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -47644,7 +47644,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -48732,7 +48732,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -49820,7 +49820,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -51996,7 +51996,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -53084,7 +53084,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -55112,7 +55112,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -56744,7 +56744,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -58376,7 +58376,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60008,7 +60008,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61640,7 +61640,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -63272,7 +63272,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -64904,7 +64904,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66536,7 +66536,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -68168,7 +68168,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -69652,7 +69652,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71284,7 +71284,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -72768,7 +72768,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74400,7 +74400,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -75636,7 +75636,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -76872,7 +76872,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -78108,7 +78108,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -79344,7 +79344,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
@@ -80580,7 +80580,7 @@
       </c>
       <c r="AJ440" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK440" t="inlineStr">
@@ -81668,7 +81668,7 @@
       </c>
       <c r="AJ446" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK446" t="inlineStr">
@@ -82756,7 +82756,7 @@
       </c>
       <c r="AJ452" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK452" t="inlineStr">
@@ -83992,7 +83992,7 @@
       </c>
       <c r="AJ459" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK459" t="inlineStr">
@@ -85080,7 +85080,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -86316,7 +86316,7 @@
       </c>
       <c r="AJ472" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK472" t="inlineStr">

--- a/diseases/d040/2005-2009.xlsx
+++ b/diseases/d040/2005-2009.xlsx
@@ -1161,9 +1161,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1702,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2101,9 +2095,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3041,9 +3029,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3585,9 +3570,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3733,9 +3715,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4525,9 +4504,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5069,9 +5045,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5217,9 +5190,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -6009,9 +5979,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6553,9 +6520,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6701,9 +6665,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7641,9 +7602,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -8185,9 +8143,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8333,9 +8288,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -9273,9 +9225,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9817,9 +9766,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9965,9 +9911,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10905,9 +10848,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11449,9 +11389,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11597,9 +11534,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12537,9 +12471,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13081,9 +13012,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13229,9 +13157,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14021,9 +13946,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14565,9 +14487,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14713,9 +14632,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -15505,9 +15421,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -16049,9 +15962,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16197,9 +16107,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16989,9 +16896,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17533,9 +17437,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17681,9 +17582,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18621,9 +18519,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -19165,9 +19060,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19313,9 +19205,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -20253,9 +20142,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20797,9 +20683,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -21193,9 +21076,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21341,9 +21221,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -22133,9 +22010,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22677,9 +22551,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -22825,9 +22696,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23765,9 +23633,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -24309,9 +24174,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -24457,9 +24319,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -25249,9 +25108,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -25793,9 +25649,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -25941,9 +25794,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26733,9 +26583,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -27277,9 +27124,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27425,9 +27269,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -28365,9 +28206,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -28909,9 +28747,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -29057,9 +28892,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -29849,9 +29681,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -30393,9 +30222,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -30541,9 +30367,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -31333,9 +31156,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -31877,9 +31697,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -32025,9 +31842,6 @@
       <c r="O172" t="n">
         <v>2</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -32817,9 +32631,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -33361,9 +33172,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -33509,9 +33317,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -34449,9 +34254,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -34993,9 +34795,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -35141,9 +34940,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -35933,9 +35729,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -36477,9 +36270,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -36625,9 +36415,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -37565,9 +37352,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -38109,9 +37893,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -38257,9 +38038,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -39049,9 +38827,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -39593,9 +39368,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -39989,9 +39761,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -40681,9 +40450,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -41225,9 +40991,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -41769,9 +41532,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -42313,9 +42073,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -43005,9 +42762,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -43549,9 +43303,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -44093,9 +43844,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -44637,9 +44385,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -45329,9 +45074,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -45873,9 +45615,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -46565,9 +46304,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -47109,9 +46845,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -47801,9 +47534,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -48345,9 +48075,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -48889,9 +48616,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -49433,9 +49157,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -49977,9 +49698,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -50521,9 +50239,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -51065,9 +50780,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -51609,9 +51321,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -52153,9 +51862,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -52697,9 +52403,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -53241,9 +52944,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -53785,9 +53485,6 @@
       <c r="O292" t="n">
         <v>1</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.3149462465493702</v>
       </c>
@@ -54181,9 +53878,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -54329,9 +54023,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -55269,9 +54960,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -55813,9 +55501,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -55961,9 +55646,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -56901,9 +56583,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -57445,9 +57124,6 @@
       <c r="O312" t="n">
         <v>0</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0</v>
       </c>
@@ -57593,9 +57269,6 @@
       <c r="O313" t="n">
         <v>1</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -58533,9 +58206,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -59077,9 +58747,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -59225,9 +58892,6 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
@@ -60165,9 +59829,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -60709,9 +60370,6 @@
       <c r="O330" t="n">
         <v>0</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0</v>
       </c>
@@ -60857,9 +60515,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -61797,9 +61452,6 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0</v>
       </c>
@@ -62341,9 +61993,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -62489,9 +62138,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -63429,9 +63075,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -63973,9 +63616,6 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
@@ -64121,9 +63761,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -65061,9 +64698,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -65605,9 +65239,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -65753,9 +65384,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -66693,9 +66321,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -67237,9 +66862,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -67385,9 +67007,6 @@
       <c r="O367" t="n">
         <v>0</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
@@ -68325,9 +67944,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -68869,9 +68485,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -69017,9 +68630,6 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
@@ -69809,9 +69419,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -70353,9 +69960,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -70501,9 +70105,6 @@
       <c r="O384" t="n">
         <v>0</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0</v>
       </c>
@@ -71441,9 +71042,6 @@
       <c r="O389" t="n">
         <v>0</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0</v>
       </c>
@@ -71985,9 +71583,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -72133,9 +71728,6 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0</v>
       </c>
@@ -72925,9 +72517,6 @@
       <c r="O397" t="n">
         <v>0</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0</v>
       </c>
@@ -73469,9 +73058,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -73865,9 +73451,6 @@
       <c r="O402" t="n">
         <v>0</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0</v>
       </c>
@@ -74557,9 +74140,6 @@
       <c r="O406" t="n">
         <v>0</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0</v>
       </c>
@@ -75101,9 +74681,6 @@
       <c r="O409" t="n">
         <v>0</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0</v>
       </c>
@@ -75793,9 +75370,6 @@
       <c r="O413" t="n">
         <v>0</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0</v>
       </c>
@@ -76337,9 +75911,6 @@
       <c r="O416" t="n">
         <v>0</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0</v>
       </c>
@@ -77029,9 +76600,6 @@
       <c r="O420" t="n">
         <v>0</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0</v>
       </c>
@@ -77573,9 +77141,6 @@
       <c r="O423" t="n">
         <v>0</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0</v>
       </c>
@@ -78265,9 +77830,6 @@
       <c r="O427" t="n">
         <v>0</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0</v>
       </c>
@@ -78809,9 +78371,6 @@
       <c r="O430" t="n">
         <v>0</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0</v>
       </c>
@@ -79501,9 +79060,6 @@
       <c r="O434" t="n">
         <v>0</v>
       </c>
-      <c r="Q434" t="n">
-        <v>0</v>
-      </c>
       <c r="R434" t="n">
         <v>0</v>
       </c>
@@ -80045,9 +79601,6 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
       <c r="R437" t="n">
         <v>0</v>
       </c>
@@ -80737,9 +80290,6 @@
       <c r="O441" t="n">
         <v>0</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0</v>
       </c>
@@ -81281,9 +80831,6 @@
       <c r="O444" t="n">
         <v>0</v>
       </c>
-      <c r="Q444" t="n">
-        <v>0</v>
-      </c>
       <c r="R444" t="n">
         <v>0</v>
       </c>
@@ -81825,9 +81372,6 @@
       <c r="O447" t="n">
         <v>0</v>
       </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
       <c r="R447" t="n">
         <v>0</v>
       </c>
@@ -82369,9 +81913,6 @@
       <c r="O450" t="n">
         <v>0</v>
       </c>
-      <c r="Q450" t="n">
-        <v>0</v>
-      </c>
       <c r="R450" t="n">
         <v>0</v>
       </c>
@@ -82913,9 +82454,6 @@
       <c r="O453" t="n">
         <v>0</v>
       </c>
-      <c r="Q453" t="n">
-        <v>0</v>
-      </c>
       <c r="R453" t="n">
         <v>0</v>
       </c>
@@ -83457,9 +82995,6 @@
       <c r="O456" t="n">
         <v>0</v>
       </c>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
       <c r="R456" t="n">
         <v>0</v>
       </c>
@@ -84149,9 +83684,6 @@
       <c r="O460" t="n">
         <v>0</v>
       </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
       <c r="R460" t="n">
         <v>0</v>
       </c>
@@ -84693,9 +84225,6 @@
       <c r="O463" t="n">
         <v>0</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0</v>
       </c>
@@ -85237,9 +84766,6 @@
       <c r="O466" t="n">
         <v>0</v>
       </c>
-      <c r="Q466" t="n">
-        <v>0</v>
-      </c>
       <c r="R466" t="n">
         <v>0</v>
       </c>
@@ -85781,9 +85307,6 @@
       <c r="O469" t="n">
         <v>0</v>
       </c>
-      <c r="Q469" t="n">
-        <v>0</v>
-      </c>
       <c r="R469" t="n">
         <v>0</v>
       </c>
@@ -86473,9 +85996,6 @@
       <c r="O473" t="n">
         <v>0</v>
       </c>
-      <c r="Q473" t="n">
-        <v>0</v>
-      </c>
       <c r="R473" t="n">
         <v>0</v>
       </c>
@@ -87015,9 +86535,6 @@
         <v>0</v>
       </c>
       <c r="O476" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q476" t="n">
         <v>0</v>
       </c>
       <c r="R476" t="n">

--- a/diseases/d040/2005-2009.xlsx
+++ b/diseases/d040/2005-2009.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16749,7 +16749,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -29534,7 +29534,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -37205,7 +37205,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -38680,7 +38680,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -40303,7 +40303,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -42615,7 +42615,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -43697,7 +43697,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -44927,7 +44927,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -46157,7 +46157,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -47387,7 +47387,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -48469,7 +48469,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -49551,7 +49551,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -50633,7 +50633,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -51715,7 +51715,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -54813,7 +54813,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -56436,7 +56436,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -58059,7 +58059,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -59682,7 +59682,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -61305,7 +61305,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -62928,7 +62928,7 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN344" t="b">
@@ -64551,7 +64551,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -66174,7 +66174,7 @@
       </c>
       <c r="AM362" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN362" t="b">
@@ -67797,7 +67797,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -69272,7 +69272,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -70895,7 +70895,7 @@
       </c>
       <c r="AM388" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN388" t="b">
@@ -72370,7 +72370,7 @@
       </c>
       <c r="AM396" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN396" t="b">
@@ -73993,7 +73993,7 @@
       </c>
       <c r="AM405" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN405" t="b">
@@ -75223,7 +75223,7 @@
       </c>
       <c r="AM412" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN412" t="b">
@@ -76453,7 +76453,7 @@
       </c>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN419" t="b">
@@ -77683,7 +77683,7 @@
       </c>
       <c r="AM426" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN426" t="b">
@@ -78913,7 +78913,7 @@
       </c>
       <c r="AM433" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN433" t="b">
@@ -80143,7 +80143,7 @@
       </c>
       <c r="AM440" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN440" t="b">
@@ -81225,7 +81225,7 @@
       </c>
       <c r="AM446" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN446" t="b">
@@ -82307,7 +82307,7 @@
       </c>
       <c r="AM452" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN452" t="b">
@@ -83537,7 +83537,7 @@
       </c>
       <c r="AM459" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN459" t="b">
@@ -84619,7 +84619,7 @@
       </c>
       <c r="AM465" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN465" t="b">
@@ -85849,7 +85849,7 @@
       </c>
       <c r="AM472" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN472" t="b">

--- a/diseases/d040/2005-2009.xlsx
+++ b/diseases/d040/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21853,7 +21853,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30999,7 +30999,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40293,7 +40293,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -41375,7 +41375,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -42605,7 +42605,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -43687,7 +43687,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -44917,7 +44917,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46147,7 +46147,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -47377,7 +47377,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -49541,7 +49541,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -50623,7 +50623,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -51705,7 +51705,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52787,7 +52787,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -54803,7 +54803,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -56426,7 +56426,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -58049,7 +58049,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -59672,7 +59672,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61295,7 +61295,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62918,7 +62918,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -64541,7 +64541,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66164,7 +66164,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -67787,7 +67787,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -69262,7 +69262,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -70885,7 +70885,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -72360,7 +72360,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -73983,7 +73983,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -75213,7 +75213,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -76443,7 +76443,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -77673,7 +77673,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -78903,7 +78903,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
@@ -80133,7 +80133,7 @@
       </c>
       <c r="AJ440" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK440" t="inlineStr">
@@ -81215,7 +81215,7 @@
       </c>
       <c r="AJ446" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK446" t="inlineStr">
@@ -82297,7 +82297,7 @@
       </c>
       <c r="AJ452" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK452" t="inlineStr">
@@ -83527,7 +83527,7 @@
       </c>
       <c r="AJ459" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK459" t="inlineStr">
@@ -84609,7 +84609,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -85839,7 +85839,7 @@
       </c>
       <c r="AJ472" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK472" t="inlineStr">
